--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="4356" windowHeight="4896"/>
   </bookViews>
   <sheets>
     <sheet name="Bug_Log" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="61">
   <si>
     <t>Bug ID</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>nightly_reg_01</t>
   </si>
   <si>
     <t>High</t>
@@ -183,6 +180,37 @@
   </si>
   <si>
     <t>23 us</t>
+  </si>
+  <si>
+    <t>RTL_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX PAD with NO CRC</t>
+  </si>
+  <si>
+    <t>Continous sending of padding bytes</t>
+  </si>
+  <si>
+    <t>eth_test_tx_moder</t>
+  </si>
+  <si>
+    <t>1735803809
+2085910529</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>rg_01_tx_moder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+When PKTLEN &lt; MINFL and effective pad &amp; crc is PAD = 1 CRC =0, DUT sends infinite padding 0s  
+</t>
   </si>
 </sst>
 </file>
@@ -203,7 +231,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,8 +243,14 @@
         <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -224,21 +258,427 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -252,25 +692,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P2">
-  <autoFilter ref="A1:P2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P3" dataDxfId="16">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
-    <tableColumn id="1" name="Bug ID"/>
-    <tableColumn id="2" name="Date Found"/>
-    <tableColumn id="3" name="Found By"/>
-    <tableColumn id="4" name="Module / Block"/>
-    <tableColumn id="5" name="Feature"/>
-    <tableColumn id="6" name="Bug Summary"/>
-    <tableColumn id="7" name="Detailed Description"/>
-    <tableColumn id="8" name="Severity"/>
-    <tableColumn id="12" name="Test Name"/>
-    <tableColumn id="13" name="Seed"/>
-    <tableColumn id="14" name="Simulation Time"/>
-    <tableColumn id="15" name="Failure Type"/>
-    <tableColumn id="16" name="Waveform Available"/>
-    <tableColumn id="17" name="Root Cause"/>
-    <tableColumn id="21" name="Regression Run"/>
-    <tableColumn id="22" name="Comments"/>
+    <tableColumn id="1" name="Bug ID" dataDxfId="15"/>
+    <tableColumn id="2" name="Date Found" dataDxfId="14"/>
+    <tableColumn id="3" name="Found By" dataDxfId="13"/>
+    <tableColumn id="4" name="Module / Block" dataDxfId="12"/>
+    <tableColumn id="5" name="Feature" dataDxfId="11"/>
+    <tableColumn id="6" name="Bug Summary" dataDxfId="10"/>
+    <tableColumn id="7" name="Detailed Description" dataDxfId="9"/>
+    <tableColumn id="8" name="Severity" dataDxfId="8"/>
+    <tableColumn id="12" name="Test Name" dataDxfId="7"/>
+    <tableColumn id="13" name="Seed" dataDxfId="6"/>
+    <tableColumn id="14" name="Simulation Time" dataDxfId="5"/>
+    <tableColumn id="15" name="Failure Type" dataDxfId="4"/>
+    <tableColumn id="16" name="Waveform Available" dataDxfId="3"/>
+    <tableColumn id="17" name="Root Cause" dataDxfId="2"/>
+    <tableColumn id="21" name="Regression Run" dataDxfId="1"/>
+    <tableColumn id="22" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -561,20 +1001,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
     <col min="4" max="4" width="17.21875" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="24.77734375" customWidth="1"/>
     <col min="9" max="9" width="19.44140625" customWidth="1"/>
-    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" customWidth="1"/>
     <col min="11" max="11" width="8.77734375" customWidth="1"/>
     <col min="12" max="12" width="11.44140625" customWidth="1"/>
-    <col min="13" max="13" width="6.44140625" customWidth="1"/>
+    <col min="13" max="13" width="6.5546875" customWidth="1"/>
     <col min="14" max="14" width="21.6640625" customWidth="1"/>
     <col min="15" max="15" width="16.88671875" customWidth="1"/>
     <col min="16" max="16" width="26.21875" customWidth="1"/>
@@ -631,54 +1071,102 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="O2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="7">
+        <v>46218</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="I3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" t="s">
-        <v>46</v>
-      </c>
+      <c r="N3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -693,19 +1181,19 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H499</xm:sqref>
+          <xm:sqref>H2:H500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L499</xm:sqref>
+          <xm:sqref>L2:L500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M499</xm:sqref>
+          <xm:sqref>M2:M500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -729,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
         <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -743,10 +1231,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>24</v>
@@ -754,60 +1242,60 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
         <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>Bug ID</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>RTL_001</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
   </si>
   <si>
     <t>Critical</t>
@@ -172,10 +169,6 @@
   </si>
   <si>
     <t xml:space="preserve">
-TX NO Preamble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
 Preamble is sent </t>
   </si>
   <si>
@@ -185,32 +178,69 @@
     <t>RTL_002</t>
   </si>
   <si>
-    <t xml:space="preserve">
-TX PAD with NO CRC</t>
-  </si>
-  <si>
     <t>Continous sending of padding bytes</t>
   </si>
   <si>
     <t>eth_test_tx_moder</t>
   </si>
   <si>
-    <t>1735803809
-2085910529</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Unknown</t>
-  </si>
-  <si>
-    <t>rg_01_tx_moder</t>
   </si>
   <si>
     <t xml:space="preserve">
 When PKTLEN &lt; MINFL and effective pad &amp; crc is PAD = 1 CRC =0, DUT sends infinite padding 0s  
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1735803809
+</t>
+  </si>
+  <si>
+    <t>RTL_003</t>
+  </si>
+  <si>
+    <t>tc_06_tx_moder</t>
+  </si>
+  <si>
+    <t>tc_07_tx_ipgt</t>
+  </si>
+  <si>
+    <t>tc_01_tx_nopre</t>
+  </si>
+  <si>
+    <t>14/7/2026</t>
+  </si>
+  <si>
+    <t>eth_test_tx_ipgt</t>
+  </si>
+  <si>
+    <t>TX - Full duplex - IPGT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX - PAD - NO CRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX - NO Preamble</t>
+  </si>
+  <si>
+    <t>In full duplex mode actual gap time  is less than IPGT value</t>
+  </si>
+  <si>
+    <t>8660 ns</t>
+  </si>
+  <si>
+    <t>In Full duplex mode  after packet transmission the gap time until next packet is less than value in IPGT register by 3 clock cycles</t>
+  </si>
+  <si>
+    <t>Pipeline in logic / mistake in specs</t>
+  </si>
+  <si>
+    <t>15/7/2026</t>
   </si>
 </sst>
 </file>
@@ -290,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -302,7 +332,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,323 +362,75 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -640,34 +439,270 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal style="thin">
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
           <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
+        </top>
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
-        <bottom style="thin">
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal style="thin">
+        </top>
+        <bottom style="thin">
           <color auto="1"/>
-        </horizontal>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -692,25 +727,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P3" dataDxfId="16">
-  <autoFilter ref="A1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P4" dataDxfId="16">
+  <autoFilter ref="A1:P4"/>
   <tableColumns count="16">
-    <tableColumn id="1" name="Bug ID" dataDxfId="15"/>
-    <tableColumn id="2" name="Date Found" dataDxfId="14"/>
-    <tableColumn id="3" name="Found By" dataDxfId="13"/>
-    <tableColumn id="4" name="Module / Block" dataDxfId="12"/>
-    <tableColumn id="5" name="Feature" dataDxfId="11"/>
-    <tableColumn id="6" name="Bug Summary" dataDxfId="10"/>
-    <tableColumn id="7" name="Detailed Description" dataDxfId="9"/>
-    <tableColumn id="8" name="Severity" dataDxfId="8"/>
-    <tableColumn id="12" name="Test Name" dataDxfId="7"/>
-    <tableColumn id="13" name="Seed" dataDxfId="6"/>
-    <tableColumn id="14" name="Simulation Time" dataDxfId="5"/>
-    <tableColumn id="15" name="Failure Type" dataDxfId="4"/>
-    <tableColumn id="16" name="Waveform Available" dataDxfId="3"/>
-    <tableColumn id="17" name="Root Cause" dataDxfId="2"/>
-    <tableColumn id="21" name="Regression Run" dataDxfId="1"/>
-    <tableColumn id="22" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" name="Bug ID" dataDxfId="5"/>
+    <tableColumn id="2" name="Date Found" dataDxfId="3"/>
+    <tableColumn id="3" name="Found By" dataDxfId="4"/>
+    <tableColumn id="4" name="Module / Block" dataDxfId="2"/>
+    <tableColumn id="5" name="Feature" dataDxfId="0"/>
+    <tableColumn id="6" name="Bug Summary" dataDxfId="1"/>
+    <tableColumn id="7" name="Detailed Description" dataDxfId="15"/>
+    <tableColumn id="8" name="Severity" dataDxfId="14"/>
+    <tableColumn id="12" name="Test Name" dataDxfId="13"/>
+    <tableColumn id="13" name="Seed" dataDxfId="12"/>
+    <tableColumn id="14" name="Simulation Time" dataDxfId="11"/>
+    <tableColumn id="15" name="Failure Type" dataDxfId="10"/>
+    <tableColumn id="16" name="Waveform Available" dataDxfId="9"/>
+    <tableColumn id="17" name="Root Cause" dataDxfId="8"/>
+    <tableColumn id="21" name="Regression Run" dataDxfId="7"/>
+    <tableColumn id="22" name="Comments" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1001,13 +1036,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
     <col min="4" max="4" width="17.21875" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" customWidth="1"/>
     <col min="9" max="9" width="19.44140625" customWidth="1"/>
@@ -1074,99 +1109,147 @@
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="N2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B3" s="7">
-        <v>46218</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="B4" s="8">
+        <v>46302</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1845683181</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="N4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="5"/>
+      <c r="P4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1181,19 +1264,19 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H500</xm:sqref>
+          <xm:sqref>H2:H501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L500</xm:sqref>
+          <xm:sqref>L2:L501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M500</xm:sqref>
+          <xm:sqref>M2:M501</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1217,85 +1300,85 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
         <v>29</v>
-      </c>
-      <c r="E1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
       <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
         <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\C\ITI\GP\repo\doc\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="4356" windowHeight="4896"/>
   </bookViews>
@@ -20,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
   <si>
     <t>Bug ID</t>
   </si>
@@ -241,12 +236,45 @@
   </si>
   <si>
     <t>15/7/2026</t>
+  </si>
+  <si>
+    <t>RTL_004</t>
+  </si>
+  <si>
+    <t>Nada</t>
+  </si>
+  <si>
+    <t>eth_registers</t>
+  </si>
+  <si>
+    <t>eth_test_reg_access</t>
+  </si>
+  <si>
+    <t>RAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  27/6/2026  </t>
+  </si>
+  <si>
+    <t>MODER bit[11] reserved bit implemented as writable</t>
+  </si>
+  <si>
+    <t>The specification marks MODER bit[11] as reserved, but the DUT allows it to be written/read as an active bit instead of behaving as a reserved bit.</t>
+  </si>
+  <si>
+    <t>tc_01_reg</t>
+  </si>
+  <si>
+    <t>RTL design issue – Reserved bit[11] is not implemented as reserved; writes to the bit are not ignored.</t>
+  </si>
+  <si>
+    <t>MODER Register access</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -280,7 +308,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -316,11 +344,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -350,6 +393,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,7 +414,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -429,6 +480,249 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -460,248 +754,6 @@
         </top>
         <bottom style="thin">
           <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -730,22 +782,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P4" dataDxfId="16">
   <autoFilter ref="A1:P4"/>
   <tableColumns count="16">
-    <tableColumn id="1" name="Bug ID" dataDxfId="5"/>
-    <tableColumn id="2" name="Date Found" dataDxfId="3"/>
-    <tableColumn id="3" name="Found By" dataDxfId="4"/>
-    <tableColumn id="4" name="Module / Block" dataDxfId="2"/>
-    <tableColumn id="5" name="Feature" dataDxfId="0"/>
-    <tableColumn id="6" name="Bug Summary" dataDxfId="1"/>
-    <tableColumn id="7" name="Detailed Description" dataDxfId="15"/>
-    <tableColumn id="8" name="Severity" dataDxfId="14"/>
-    <tableColumn id="12" name="Test Name" dataDxfId="13"/>
-    <tableColumn id="13" name="Seed" dataDxfId="12"/>
-    <tableColumn id="14" name="Simulation Time" dataDxfId="11"/>
-    <tableColumn id="15" name="Failure Type" dataDxfId="10"/>
-    <tableColumn id="16" name="Waveform Available" dataDxfId="9"/>
-    <tableColumn id="17" name="Root Cause" dataDxfId="8"/>
-    <tableColumn id="21" name="Regression Run" dataDxfId="7"/>
-    <tableColumn id="22" name="Comments" dataDxfId="6"/>
+    <tableColumn id="1" name="Bug ID" dataDxfId="15"/>
+    <tableColumn id="2" name="Date Found" dataDxfId="14"/>
+    <tableColumn id="3" name="Found By" dataDxfId="13"/>
+    <tableColumn id="4" name="Module / Block" dataDxfId="12"/>
+    <tableColumn id="5" name="Feature" dataDxfId="11"/>
+    <tableColumn id="6" name="Bug Summary" dataDxfId="10"/>
+    <tableColumn id="7" name="Detailed Description" dataDxfId="9"/>
+    <tableColumn id="8" name="Severity" dataDxfId="8"/>
+    <tableColumn id="12" name="Test Name" dataDxfId="7"/>
+    <tableColumn id="13" name="Seed" dataDxfId="6"/>
+    <tableColumn id="14" name="Simulation Time" dataDxfId="5"/>
+    <tableColumn id="15" name="Failure Type" dataDxfId="4"/>
+    <tableColumn id="16" name="Waveform Available" dataDxfId="3"/>
+    <tableColumn id="17" name="Root Cause" dataDxfId="2"/>
+    <tableColumn id="21" name="Regression Run" dataDxfId="1"/>
+    <tableColumn id="22" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1036,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
@@ -1251,6 +1303,52 @@
       </c>
       <c r="P4" s="5"/>
     </row>
+    <row r="5" spans="1:16" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="P5" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1264,19 +1362,19 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H501</xm:sqref>
+          <xm:sqref>H2:H4 H6:H501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L501</xm:sqref>
+          <xm:sqref>L2:L4 L6:L501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M501</xm:sqref>
+          <xm:sqref>M2:M4 M6:M501</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\C\ITI\GP\repo\doc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="4356" windowHeight="4896"/>
   </bookViews>
@@ -15,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>Bug ID</t>
   </si>
@@ -269,12 +274,44 @@
   </si>
   <si>
     <t>MODER Register access</t>
+  </si>
+  <si>
+    <t>RTL_005</t>
+  </si>
+  <si>
+    <t>21/7/2026</t>
+  </si>
+  <si>
+    <t>eth_wishbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+WB_M - DATA_O - X Propagation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A
+</t>
+  </si>
+  <si>
+    <t>eth_test_tx_smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X propagation after Reset assertion </t>
+  </si>
+  <si>
+    <t>tc_01_smoke</t>
+  </si>
+  <si>
+    <t>In wishbone master when reset is asserted, DATA_O is unknown (x)</t>
+  </si>
+  <si>
+    <t>2.5 ns</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -289,7 +326,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,8 +344,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -359,48 +402,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -414,6 +501,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -480,6 +568,30 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -634,29 +746,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -779,25 +868,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P4" dataDxfId="16">
-  <autoFilter ref="A1:P4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P6" dataDxfId="16">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Bug ID" dataDxfId="15"/>
     <tableColumn id="2" name="Date Found" dataDxfId="14"/>
     <tableColumn id="3" name="Found By" dataDxfId="13"/>
     <tableColumn id="4" name="Module / Block" dataDxfId="12"/>
-    <tableColumn id="5" name="Feature" dataDxfId="11"/>
-    <tableColumn id="6" name="Bug Summary" dataDxfId="10"/>
-    <tableColumn id="7" name="Detailed Description" dataDxfId="9"/>
-    <tableColumn id="8" name="Severity" dataDxfId="8"/>
-    <tableColumn id="12" name="Test Name" dataDxfId="7"/>
-    <tableColumn id="13" name="Seed" dataDxfId="6"/>
-    <tableColumn id="14" name="Simulation Time" dataDxfId="5"/>
-    <tableColumn id="15" name="Failure Type" dataDxfId="4"/>
-    <tableColumn id="16" name="Waveform Available" dataDxfId="3"/>
-    <tableColumn id="17" name="Root Cause" dataDxfId="2"/>
-    <tableColumn id="21" name="Regression Run" dataDxfId="1"/>
-    <tableColumn id="22" name="Comments" dataDxfId="0"/>
+    <tableColumn id="5" name="Feature" dataDxfId="4"/>
+    <tableColumn id="6" name="Bug Summary" dataDxfId="3"/>
+    <tableColumn id="7" name="Detailed Description" dataDxfId="2"/>
+    <tableColumn id="8" name="Severity" dataDxfId="0"/>
+    <tableColumn id="12" name="Test Name" dataDxfId="1"/>
+    <tableColumn id="13" name="Seed" dataDxfId="11"/>
+    <tableColumn id="14" name="Simulation Time" dataDxfId="10"/>
+    <tableColumn id="15" name="Failure Type" dataDxfId="9"/>
+    <tableColumn id="16" name="Waveform Available" dataDxfId="8"/>
+    <tableColumn id="17" name="Root Cause" dataDxfId="7"/>
+    <tableColumn id="21" name="Regression Run" dataDxfId="6"/>
+    <tableColumn id="22" name="Comments" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1088,13 +1177,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
     <col min="4" max="4" width="17.21875" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" customWidth="1"/>
     <col min="9" max="9" width="19.44140625" customWidth="1"/>
@@ -1157,197 +1246,245 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>61</v>
+      <c r="B2" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>73</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>32</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>22</v>
+        <v>74</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>46</v>
+      <c r="N2" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:16" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="E3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1845683181</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" s="5"/>
+      <c r="N3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="8">
-        <v>46302</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" s="6">
-        <v>1845683181</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="E4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="12">
+        <v>1</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P4" s="5"/>
+      <c r="N4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:16" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="B5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="L5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="P5" s="4"/>
+      <c r="N5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="13"/>
+    </row>
+    <row r="6" spans="1:16" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="P6" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1362,19 +1499,19 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H4 H6:H501</xm:sqref>
+          <xm:sqref>H3:H6 H8:H501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L4 L6:L501</xm:sqref>
+          <xm:sqref>L2:L6 L8:L501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M4 M6:M501</xm:sqref>
+          <xm:sqref>M3:M6 M8:M501</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1384,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1476,6 +1613,11 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
         <v>41</v>
       </c>
     </row>

--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -15,12 +15,12 @@
     <sheet name="Bug_Log" sheetId="1" r:id="rId1"/>
     <sheet name="Lists" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="102">
   <si>
     <t>Bug ID</t>
   </si>
@@ -306,6 +306,37 @@
   </si>
   <si>
     <t>2.5 ns</t>
+  </si>
+  <si>
+    <t>DATA_O is assigned to uninitialized FIFO</t>
+  </si>
+  <si>
+    <t>RTL_006</t>
+  </si>
+  <si>
+    <t>22/7/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX - MAXFL </t>
+  </si>
+  <si>
+    <t>Frame is sent when maxfl &lt;=4 bytes</t>
+  </si>
+  <si>
+    <t>eth_test_tx_maxfl</t>
+  </si>
+  <si>
+    <t>tc_10_maxfl</t>
+  </si>
+  <si>
+    <t>Specs states that frames with length = 4bytes or less aren't sent, when maxfl is  4 or less , the configured number is sent and rest of frame is discarded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUT doesn't check maxfl &gt; 4 bytes </t>
+  </si>
+  <si>
+    <t>eth_txethmac</t>
   </si>
 </sst>
 </file>
@@ -501,7 +532,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -524,6 +554,161 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -592,160 +777,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -868,25 +899,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P6" dataDxfId="16">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P7" dataDxfId="16">
+  <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Bug ID" dataDxfId="15"/>
     <tableColumn id="2" name="Date Found" dataDxfId="14"/>
     <tableColumn id="3" name="Found By" dataDxfId="13"/>
     <tableColumn id="4" name="Module / Block" dataDxfId="12"/>
-    <tableColumn id="5" name="Feature" dataDxfId="4"/>
-    <tableColumn id="6" name="Bug Summary" dataDxfId="3"/>
-    <tableColumn id="7" name="Detailed Description" dataDxfId="2"/>
-    <tableColumn id="8" name="Severity" dataDxfId="0"/>
-    <tableColumn id="12" name="Test Name" dataDxfId="1"/>
-    <tableColumn id="13" name="Seed" dataDxfId="11"/>
-    <tableColumn id="14" name="Simulation Time" dataDxfId="10"/>
-    <tableColumn id="15" name="Failure Type" dataDxfId="9"/>
-    <tableColumn id="16" name="Waveform Available" dataDxfId="8"/>
-    <tableColumn id="17" name="Root Cause" dataDxfId="7"/>
-    <tableColumn id="21" name="Regression Run" dataDxfId="6"/>
-    <tableColumn id="22" name="Comments" dataDxfId="5"/>
+    <tableColumn id="5" name="Feature" dataDxfId="11"/>
+    <tableColumn id="6" name="Bug Summary" dataDxfId="10"/>
+    <tableColumn id="7" name="Detailed Description" dataDxfId="9"/>
+    <tableColumn id="8" name="Severity" dataDxfId="8"/>
+    <tableColumn id="12" name="Test Name" dataDxfId="7"/>
+    <tableColumn id="13" name="Seed" dataDxfId="6"/>
+    <tableColumn id="14" name="Simulation Time" dataDxfId="5"/>
+    <tableColumn id="15" name="Failure Type" dataDxfId="4"/>
+    <tableColumn id="16" name="Waveform Available" dataDxfId="3"/>
+    <tableColumn id="17" name="Root Cause" dataDxfId="2"/>
+    <tableColumn id="21" name="Regression Run" dataDxfId="1"/>
+    <tableColumn id="22" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1177,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
@@ -1185,7 +1216,7 @@
     <col min="4" max="4" width="17.21875" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="24.77734375" customWidth="1"/>
+    <col min="7" max="7" width="26.44140625" customWidth="1"/>
     <col min="9" max="9" width="19.44140625" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
     <col min="11" max="11" width="8.77734375" customWidth="1"/>
@@ -1351,7 +1382,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>65</v>
@@ -1425,7 +1456,7 @@
         <v>53</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>23</v>
@@ -1479,12 +1510,60 @@
         <v>23</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="O6" s="13" t="s">
         <v>89</v>
       </c>
       <c r="P6" s="13"/>
+    </row>
+    <row r="7" spans="1:16" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="P7" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1499,19 +1578,19 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H6 H8:H501</xm:sqref>
+          <xm:sqref>H3:H501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L6 L8:L501</xm:sqref>
+          <xm:sqref>L2:L501</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M3:M6 M8:M501</xm:sqref>
+          <xm:sqref>M3:M501</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
   <si>
     <t>Bug ID</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Seed</t>
   </si>
   <si>
-    <t>Simulation Time</t>
-  </si>
-  <si>
     <t>Failure Type</t>
   </si>
   <si>
@@ -161,18 +158,10 @@
   </si>
   <si>
     <t>nopre bit in reg file isn't connected to any logic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-When nopre is set to 1 in register file preamble is sent 
-</t>
   </si>
   <si>
     <t xml:space="preserve">
 Preamble is sent </t>
-  </si>
-  <si>
-    <t>23 us</t>
   </si>
   <si>
     <t>RTL_002</t>
@@ -208,9 +197,6 @@
     <t>tc_07_tx_ipgt</t>
   </si>
   <si>
-    <t>tc_01_tx_nopre</t>
-  </si>
-  <si>
     <t>14/7/2026</t>
   </si>
   <si>
@@ -231,12 +217,6 @@
     <t>In full duplex mode actual gap time  is less than IPGT value</t>
   </si>
   <si>
-    <t>8660 ns</t>
-  </si>
-  <si>
-    <t>In Full duplex mode  after packet transmission the gap time until next packet is less than value in IPGT register by 3 clock cycles</t>
-  </si>
-  <si>
     <t>Pipeline in logic / mistake in specs</t>
   </si>
   <si>
@@ -305,9 +285,6 @@
     <t>In wishbone master when reset is asserted, DATA_O is unknown (x)</t>
   </si>
   <si>
-    <t>2.5 ns</t>
-  </si>
-  <si>
     <t>DATA_O is assigned to uninitialized FIFO</t>
   </si>
   <si>
@@ -330,13 +307,58 @@
     <t>tc_10_maxfl</t>
   </si>
   <si>
-    <t>Specs states that frames with length = 4bytes or less aren't sent, when maxfl is  4 or less , the configured number is sent and rest of frame is discarded</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUT doesn't check maxfl &gt; 4 bytes </t>
   </si>
   <si>
     <t>eth_txethmac</t>
+  </si>
+  <si>
+    <t>RTL_007</t>
+  </si>
+  <si>
+    <t>31/7/2026</t>
+  </si>
+  <si>
+    <t>eth_txcounters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX - Deferral </t>
+  </si>
+  <si>
+    <t>eth_test_tx_df</t>
+  </si>
+  <si>
+    <t>When nopre is set to 1 in register file preamble is sent, this contradicts with spec which states that preamble shouldn't be sent</t>
+  </si>
+  <si>
+    <t>Next frame isn't sent after abort of previous</t>
+  </si>
+  <si>
+    <t>tc_11_df</t>
+  </si>
+  <si>
+    <t>After reaching deferral limit Nibble counter doesn't restart</t>
+  </si>
+  <si>
+    <t>test sequence is modified 
+to not produce this case to not stuck simulation</t>
+  </si>
+  <si>
+    <t>Specs states that frames with length = 4 bytes or less aren't sent, when maxfl is  4 or less , the configured number is sent and rest of frame is discarded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704648493
+</t>
+  </si>
+  <si>
+    <t>tc_02_tx_nopre</t>
+  </si>
+  <si>
+    <t>In Full duplex mode  after packet transmission the gap time until next frame is less than value in IPGT register by 3 clock cycles</t>
+  </si>
+  <si>
+    <t>When frame is aborted due to excessive deferral, the next frame isn't transmitted</t>
   </si>
 </sst>
 </file>
@@ -524,29 +546,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -899,20 +899,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:P7" dataDxfId="16">
-  <autoFilter ref="A1:P7"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="Bug ID" dataDxfId="15"/>
-    <tableColumn id="2" name="Date Found" dataDxfId="14"/>
-    <tableColumn id="3" name="Found By" dataDxfId="13"/>
-    <tableColumn id="4" name="Module / Block" dataDxfId="12"/>
-    <tableColumn id="5" name="Feature" dataDxfId="11"/>
-    <tableColumn id="6" name="Bug Summary" dataDxfId="10"/>
-    <tableColumn id="7" name="Detailed Description" dataDxfId="9"/>
-    <tableColumn id="8" name="Severity" dataDxfId="8"/>
-    <tableColumn id="12" name="Test Name" dataDxfId="7"/>
-    <tableColumn id="13" name="Seed" dataDxfId="6"/>
-    <tableColumn id="14" name="Simulation Time" dataDxfId="5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:O8" dataDxfId="15">
+  <autoFilter ref="A1:O8"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="Bug ID" dataDxfId="14"/>
+    <tableColumn id="2" name="Date Found" dataDxfId="13"/>
+    <tableColumn id="3" name="Found By" dataDxfId="12"/>
+    <tableColumn id="4" name="Module / Block" dataDxfId="11"/>
+    <tableColumn id="5" name="Feature" dataDxfId="10"/>
+    <tableColumn id="6" name="Bug Summary" dataDxfId="9"/>
+    <tableColumn id="7" name="Detailed Description" dataDxfId="8"/>
+    <tableColumn id="8" name="Severity" dataDxfId="7"/>
+    <tableColumn id="12" name="Test Name" dataDxfId="6"/>
+    <tableColumn id="13" name="Seed" dataDxfId="5"/>
     <tableColumn id="15" name="Failure Type" dataDxfId="4"/>
     <tableColumn id="16" name="Waveform Available" dataDxfId="3"/>
     <tableColumn id="17" name="Root Cause" dataDxfId="2"/>
@@ -1208,26 +1207,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
     <col min="4" max="4" width="17.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" customWidth="1"/>
     <col min="7" max="7" width="26.44140625" customWidth="1"/>
     <col min="9" max="9" width="19.44140625" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="8.77734375" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" customWidth="1"/>
-    <col min="13" max="13" width="6.5546875" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.88671875" customWidth="1"/>
-    <col min="16" max="16" width="26.21875" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="6.5546875" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.88671875" customWidth="1"/>
+    <col min="15" max="15" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,297 +1271,327 @@
       <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:15" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="2"/>
     </row>
-    <row r="2" spans="1:16" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B3" s="5">
         <v>46302</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J3" s="6">
         <v>1845683181</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="P3" s="3"/>
+      <c r="M3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="F4" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>43</v>
       </c>
       <c r="J4" s="12">
         <v>1</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="L4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>44</v>
-      </c>
+      <c r="I6" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="O6" s="13"/>
     </row>
-    <row r="5" spans="1:16" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="20" t="s">
+    <row r="7" spans="1:15" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="F7" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="P6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>97</v>
-      </c>
       <c r="J7" s="15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="O7" s="13"/>
+    </row>
+    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="O7" s="13" t="s">
+      <c r="I8" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="P7" s="13"/>
+      <c r="J8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1578,19 +1606,19 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H501</xm:sqref>
+          <xm:sqref>H3:H502</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L501</xm:sqref>
+          <xm:sqref>K2:K502</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M3:M501</xm:sqref>
+          <xm:sqref>L3:L502</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1614,90 +1642,90 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
       <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
-        <v>27</v>
-      </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
       <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="126">
   <si>
     <t>Bug ID</t>
   </si>
@@ -160,10 +160,6 @@
     <t>nopre bit in reg file isn't connected to any logic</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Preamble is sent </t>
-  </si>
-  <si>
     <t>RTL_002</t>
   </si>
   <si>
@@ -174,9 +170,6 @@
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -359,6 +352,68 @@
   </si>
   <si>
     <t>When frame is aborted due to excessive deferral, the next frame isn't transmitted</t>
+  </si>
+  <si>
+    <t>RTL_009</t>
+  </si>
+  <si>
+    <t>eth_transmitcontrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX - Control</t>
+  </si>
+  <si>
+    <t>Incorrect Control frame length</t>
+  </si>
+  <si>
+    <t>eth_test_tx_ctrl_flow</t>
+  </si>
+  <si>
+    <t>When control frame is sent and delay crc is enabled, instead of sending 64 byte frame, it sends frame has length = maximum frame length</t>
+  </si>
+  <si>
+    <t>tc_13_ctrl_flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2087696145
+</t>
+  </si>
+  <si>
+    <t>DCRC counter gets stuck at 4, results in disabling the control-frame byte counter and causing transmission to continue until the maximum frame length</t>
+  </si>
+  <si>
+    <t>DUT pads forever because StatePAD can exit only through CRC generation, while the CRC=0 completion logic lacks a StatePAD &amp;&amp; NibbleMinFl condition.</t>
+  </si>
+  <si>
+    <t>RTL_010</t>
+  </si>
+  <si>
+    <t>tc_18_ptr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX - Wishbone</t>
+  </si>
+  <si>
+    <t>Incorrect transmitted byte when pointer%4==3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Preamble of frame is sent </t>
+  </si>
+  <si>
+    <t>Missing Flop qualification updates TxData between MII nibbles, combining the correct low nibble with the next byte’s high nibble</t>
+  </si>
+  <si>
+    <t>When configuring buffer descriptor pointer with ptr%4=3, the first byte is sent wrong, it sends the low nibble combined with high nibble of the next byte  (e.g., 0x24 → 0xC4).</t>
+  </si>
+  <si>
+    <t>eth_test_tx_ptr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1329170005
+</t>
   </si>
 </sst>
 </file>
@@ -899,8 +954,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:O8" dataDxfId="15">
-  <autoFilter ref="A1:O8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugTable" displayName="BugTable" ref="A1:O10" dataDxfId="15">
+  <autoFilter ref="A1:O10"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Bug ID" dataDxfId="14"/>
     <tableColumn id="2" name="Date Found" dataDxfId="13"/>
@@ -1207,12 +1262,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" customWidth="1"/>
     <col min="7" max="7" width="26.44140625" customWidth="1"/>
@@ -1220,7 +1275,7 @@
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
     <col min="11" max="11" width="11.44140625" customWidth="1"/>
     <col min="12" max="12" width="6.5546875" customWidth="1"/>
-    <col min="13" max="13" width="21.6640625" customWidth="1"/>
+    <col min="13" max="13" width="24.5546875" customWidth="1"/>
     <col min="14" max="14" width="16.88671875" customWidth="1"/>
     <col min="15" max="15" width="26.21875" customWidth="1"/>
   </cols>
@@ -1272,54 +1327,54 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="H2" s="21" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="5">
         <v>46302</v>
@@ -1331,19 +1386,19 @@
         <v>44</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J3" s="6">
         <v>1845683181</v>
@@ -1355,34 +1410,34 @@
         <v>22</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>18</v>
@@ -1403,18 +1458,18 @@
         <v>45</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O4" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>41</v>
@@ -1423,22 +1478,22 @@
         <v>44</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>33</v>
@@ -1447,45 +1502,45 @@
         <v>22</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F6" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>82</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>84</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>26</v>
@@ -1494,43 +1549,43 @@
         <v>22</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O6" s="13"/>
     </row>
     <row r="7" spans="1:15" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K7" s="13" t="s">
         <v>21</v>
@@ -1539,43 +1594,43 @@
         <v>22</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K8" s="13" t="s">
         <v>33</v>
@@ -1584,14 +1639,104 @@
         <v>22</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="O8" s="16" t="s">
-        <v>103</v>
-      </c>
+    </row>
+    <row r="9" spans="1:15" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="14">
+        <v>46061</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="O9" s="16"/>
+    </row>
+    <row r="10" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="14">
+        <v>46061</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="O10" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1606,19 +1751,19 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H502</xm:sqref>
+          <xm:sqref>H3:H504</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K502</xm:sqref>
+          <xm:sqref>K2:K504</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>L3:L502</xm:sqref>
+          <xm:sqref>L3:L504</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1720,7 +1865,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">

--- a/doc/RTL_Bug_Tracking.xlsx
+++ b/doc/RTL_Bug_Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="153">
   <si>
     <t>Bug ID</t>
   </si>
@@ -521,10 +521,39 @@
     <t>regression_reg_tx_miim</t>
   </si>
   <si>
-    <t xml:space="preserve">When collision occurs and nobackoff = 0, the gap time between 2 sucssesive retry transmissions can be value in IPGT Register not the value in IPGR2 register </t>
-  </si>
-  <si>
     <t>In eth_txstatem: After fsm enters StateJam, RandomEq0 isn't guaranteed to be 0 during transition to StateBackoff, and when it's 1, StateBackoff = 0, so Rule1=1, and the state machine waits gap time equal value in IPGT register.</t>
+  </si>
+  <si>
+    <t>RTL_012</t>
+  </si>
+  <si>
+    <t>17/9/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TX - Half Duplex -Collision</t>
+  </si>
+  <si>
+    <t>In half duplex When collision is detected during preamble , rd bit isn't cleared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When collision is detected and nobackoff = 0, the gap time between 2 sucssesive retry transmissions can be value in IPGT Register not the value in IPGR2 register </t>
+  </si>
+  <si>
+    <t>When collision is detected and this retry attempt is the last, RD bit in buffer descriptor isn't cleared to 0</t>
+  </si>
+  <si>
+    <t>eth_test_tx_coll_pre</t>
+  </si>
+  <si>
+    <t>tc_20_coll_pre</t>
+  </si>
+  <si>
+    <t>A preamble collision prevents the transmitter from entering StateData, so TxUsedData never asserts and TxStartFrm remains high. Because TxAbortOut is masked while TxStartFrm is high, no descriptor status write occurs and the RD bit remains set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1058268213
+</t>
   </si>
 </sst>
 </file>
@@ -990,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
@@ -1533,7 +1562,7 @@
         <v>137</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H12" s="24" t="s">
         <v>22</v>
@@ -1551,12 +1580,59 @@
         <v>26</v>
       </c>
       <c r="M12" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N12" s="26" t="s">
         <v>141</v>
       </c>
       <c r="O12" s="30"/>
+    </row>
+    <row r="13" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="N13" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="O13" s="30" t="s">
+        <v>115</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1592,13 +1668,13 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>L3:L7 L33:L500 L11 L13:L31</xm:sqref>
+          <xm:sqref>L3:L7 L33:L500 L11 L14:L31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
             <xm:f>Lists!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>L8:L10 L12</xm:sqref>
+          <xm:sqref>L8:L10 L12:L13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list">
           <x14:formula1>
